--- a/expert-system/output/vacation/vacation.xlsx
+++ b/expert-system/output/vacation/vacation.xlsx
@@ -18,6 +18,13 @@
     <sheet name="TS-Vac-Payment" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="TS-Vac-Permissions" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="TS-Vac-APIErrors" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="TS-Vac-Supplement" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="TS-Vac-Maternity" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TS-Vac-CSSettings" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="TS-Vac-CalendarMigr" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="TS-VAC-AVMultiYear" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="TS-VAC-PastDateVal" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Test Data" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Risk Assessment'!$A$3:$F$15</definedName>
@@ -29,6 +36,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-Vac-Payment'!$A$3:$J$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-Vac-Permissions'!$A$3:$J$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TS-Vac-APIErrors'!$A$3:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'TS-Vac-Supplement'!$A$3:$J$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'TS-Vac-Maternity'!$A$3:$J$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'TS-Vac-CSSettings'!$A$3:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'TS-Vac-CalendarMigr'!$A$3:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TS-VAC-AVMultiYear'!$A$3:$J$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'TS-VAC-PastDateVal'!$A$3:$J$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +50,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -89,8 +102,12 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -139,8 +156,20 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -162,11 +191,55 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -212,6 +285,35 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -608,6 +710,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -624,6 +727,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -727,12 +831,18 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>3. Test Suites</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -917,103 +1027,194 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>130</v>
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>TS-Vac-Supplement</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Supplementary Scenarios</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>TS-Vac-Maternity</t>
+        </is>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Maternity Leave Lifecycle</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>4. Key Metrics</t>
-        </is>
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>TS-Vac-CSSettings</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>CS Office Settings</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Total Test Cases</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>TS-Vac-CalendarMigr</t>
+        </is>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>Calendar Migration 2024</t>
+        </is>
+      </c>
+      <c r="C30" s="28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Known Bugs Covered</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>12 (3 HIGH NPEs, 2 HIGH accounting, 4 MEDIUM, 3 LOW)</t>
-        </is>
-      </c>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>AV=True Multi-Year Balance (#3361) — 8 cases</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Security Issues</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>4 (unprotected pages, info disclosure, missing auth, ADMIN role gap)</t>
-        </is>
-      </c>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Past-Date Validation &amp; Balance (#3369, #3360) - 5 cases</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Boundary Tests</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>8 (min duration, date cutoffs, year boundary, max duration)</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Calculation Modes</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>2 (AV=false Russian accrual, AV=true advance vacation)</t>
-        </is>
-      </c>
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="12" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>State Transitions</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>10 valid + 4 invalid transitions tested</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>4. Key Metrics</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Known Bugs Covered</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>12 (3 HIGH NPEs, 2 HIGH accounting, 4 MEDIUM, 3 LOW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Security Issues</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>4 (unprotected pages, info disclosure, missing auth, ADMIN role gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Boundary Tests</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>8 (min duration, date cutoffs, year boundary, max duration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Calculation Modes</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>2 (AV=false Russian accrual, AV=true advance vacation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>State Transitions</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>10 valid + 4 invalid transitions tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>Design Issues Referenced</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>23 from 141 total in knowledge base</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Test Data Reference</t>
         </is>
       </c>
     </row>
@@ -1032,6 +1233,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2762,6 +2970,4213 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Suite: Vacation Supplementary — SO Transfer, AV Corners, Office Sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-131</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>SO transfer mid-year — available days recalculation (AV=false)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Employee in AV=false office (Russia, norm=28).
+Has accrued 14 days (6 months worked).
+Transfer to another AV=false office with norm=24.</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1. Note employee's available vacation days before transfer.
+2. Trigger CS sync with new salary office (norm=24).
+3. Wait for vacation service sync to complete.
+4. Query GET /api/vacation/v1/vacation/days/{employeeId}.
+5. Verify formula: accruedDays = 6 × (24/12) = 12.
+6. Check: availableDays = 12 + currentYearDays + pastYearDays - 24 + futureDays.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Available days correctly recalculated using new office norm (24).
+No double counting: -normDays uses new office norm.
+If currentYearDays was initialized with old norm (28), the formula produces:
+12 + 28 - 24 = 16 (incorrect, should be 12 + 24 - 24 = 12).
+Flag if result differs from expected.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>#2789</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Day Calculation</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>KEY RISK: RegularCalculationStrategy uses current office norm for both accrual AND compensation (-normDays), but currentYearDays may have been initialized with the old office norm. Verify DB: employee_days.days for current year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-132</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>SO transfer mid-year — AV=false to AV=true office switch</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Employee in AV=false office (Russia, norm=28), 6 months worked.
+Some days already used (e.g., 5 days vacation taken).
+Transfer to AV=true office (Cyprus, norm=24).</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1. Record available days before transfer (AV=false mode: accrual-based).
+2. Trigger CS sync with new AV=true salary office.
+3. Wait for vacation service sync.
+4. GET /api/vacation/v1/vacation/days/{employeeId}.
+5. Verify calculation strategy switched to AdvanceCalculationStrategy.
+6. Check: availableDays = currentYearDays + pastYearDays + futureDays (no accrual).
+7. Verify norm deviation recalculation is now active.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Calculation strategy switches from Regular to Advance.
+Available days reflect full-year balance minus used days.
+Negative balance allowed (AV=true).
+Norm deviation recalculation activates for the employee.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>#2789, #3092</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Day Calculation</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Cross-strategy transfer is high risk — verify employee_days table is properly adjusted for the strategy change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-133</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SO transfer — employee_office year record update verification</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Employee in Office A (e.g., Saturn).
+employee_office table has record for current year with Office A.
+Transfer to Office B (e.g., Jupiter) with SAME production calendar.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: SELECT * FROM employee_office WHERE employee_id = X AND year = current_year.
+2. Trigger CS sync with new office (same calendar).
+3. DB: Verify employee_office.office_id updated to Office B.
+4. DB: Verify employee.office_id updated to Office B.
+5. Verify vacation day calculation uses new office's annual leave norm.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>employee_office record updated immediately (same calendar = safe update).
+Both employee.office_id and employee_office.office_id match new office.
+Annual leave norm from new office used in calculations.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Office Sync</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeOfficeChangedProcessor: isCalendarsAreEqual() allows immediate update when calendars match. Tests the 'safe path'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-134</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>SO transfer — different calendar mid-year (deferred update)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Employee in Office A with Russian production calendar.
+employee_office record exists for current year.
+Transfer to Office B with Cyprus production calendar.
+Current date is NOT January 1 and year is current year.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Record employee_office for current year (Office A).
+2. Trigger CS sync with new office (different calendar).
+3. DB: Check employee_office for current year.
+4. DB: Check employee_office for next year.
+5. DB: Check employee.office_id (main record).
+6. Verify vacation calculations for current year.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>employee_office for CURRENT year NOT updated (deferred — different calendar mid-year).
+employee_office for NEXT year IS updated to new office.
+employee.office_id IS updated to new office.
+Current year vacation calculations use OLD office norm.
+Next year vacation calculations use NEW office norm.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Office Sync</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>This is the known architectural decision: mid-year changes with different calendars are deferred. Verify the divergence is intentional and documented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-135</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>AV=true — next year vacation before nextYearAvailableFromMonth</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Employee in AV=true office (Cyprus).
+Current date: January 15 (before February 1 default).
+nextYearAvailableFromMonth = 2 (default).</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>1. POST /api/vacation/v1/vacation/create with startDate in next year.
+2. Verify response status and error message.
+3. Change clock to February 1.
+4. POST same vacation request.
+5. Verify success.</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Step 2: 400 error with NEXT_YEAR_VACATION_NOT_AVAILABLE on startDate.
+Step 5: Vacation created successfully — next year booking allowed after Feb 1.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>#3347, #3322</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Create Validation</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Config-driven: nextYearAvailableFromMonth. Default Feb, but verify actual config value on test env. Ticket #3322 mentions Dec-01 which conflicts with code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-136</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>AV=true — negative balance carry-over to next year</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Employee in AV=true office with negative current year balance (-3 days).
+Next year has just started.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Verify employee_days shows negative balance for previous year.
+2. GET /api/vacation/v1/vacation/days/{employeeId} — check available days.
+3. Verify AdvanceCalculationStrategy formula: currentYearDays + pastYearDays.
+4. Check if negative pastYearDays reduces current year available.
+5. Create a vacation request for current year.
+6. Verify available days account for the negative carry-over.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Negative pastYearDays from previous year correctly reduces current year available.
+Available = currentYearDays + pastYearDays (negative) + futureDays.
+Employee can still create vacations if total is positive.
+If total is negative, vacation creation should still be allowed (AV=true).</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>#3361</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Day Calculation</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>AV=true allows negative balances. Verify negative carry-over arithmetic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-137</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>AV=true — multi-year accumulated balance (3+ years)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Employee in AV=true office for 3+ years.
+Has unused days from year Y-2, Y-1, and current year Y.
+Some norm deviation adjustments in past years.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: SELECT * FROM employee_days WHERE employee_id = X ORDER BY year.
+2. GET /api/vacation/v1/vacation/days/{employeeId}.
+3. Verify formula sums all year balances: pastYearDays includes Y-2 + Y-1.
+4. Create a vacation consuming more than current year balance.
+5. Verify FIFO consumption: oldest year (Y-2) consumed first.
+6. Check remaining balances per year after vacation.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Available days = sum of all year balances (currentYearDays + pastYearDays).
+FIFO consumption: Y-2 depleted first, then Y-1, then Y.
+Norm deviation adjustments correctly reflected in each year's balance.
+No year is 'forgotten' or double-counted.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>#3361</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Day Calculation</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Test with employee who has 3+ years of data. Check employee_days for each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-138</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>AV=true — norm deviation recalculation after overtime</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Employee in AV=true office.
+Has reported more hours than personal norm for current month.
+Norm deviation type = Include both (overtime adds, undertime deducts).</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1. GET /api/vacation/v1/vacation/days/{employeeId} — record balance.
+2. Submit time reports exceeding personal norm by 16 hours (2 days).
+3. Trigger statistics recalculation.
+4. GET /api/vacation/v1/vacation/days/{employeeId} — check updated balance.
+5. Verify: daysDelta = (reported - personalNorm) / 8 = 2 days added.
+6. Check which year's balance was incremented (earliest year with capacity).</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Available days increased by 2.
+daysDelta correctly calculated: (reported - personalNorm) / REPORTING_NORM(8).
+Days added to earliest year with remaining capacity.
+If all years full, current year balance increases (can go above norm).</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>#3092</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Norm Deviation</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Hardcoded REPORTING_NORM=8. Verify with non-standard work hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-139</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Maternity begin — reject NEW vacations only, keep APPROVED</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Employee with:
+- 1 vacation in NEW status (future date)
+- 1 vacation in APPROVED status (future date)
+- 1 vacation in PAID status (past date)</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>1. Record all vacation statuses before maternity.
+2. Trigger EmployeeMaternityBeginEvent for the employee.
+3. GET /api/vacation/v1/vacation?employeeId={id} — list all vacations.
+4. Verify each vacation's status.
+5. Check employee_days for proportional reduction.
+6. Check next year days zeroed.</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>NEW vacation → REJECTED.
+APPROVED vacation → unchanged (still APPROVED).
+PAID vacation → unchanged (still PAID).
+Current year days reduced proportionally.
+Next year days set to 0.</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeMaternityBeginEventListener.onMaternityBegin() only rejects NEW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-140</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Next year vacation — boundary date (last day before unlock)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>nextYearAvailableFromMonth = 2 (February).
+Clock set to January 31 (last day before unlock).</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>1. Set clock to Jan 31.
+2. POST vacation with startDate = next year Jan 5.
+3. Verify rejection.
+4. Set clock to Feb 1.
+5. POST same vacation.
+6. Verify acceptance.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Jan 31: Rejected with NEXT_YEAR_VACATION_NOT_AVAILABLE.
+Feb 1: Accepted — next year booking now available.
+Boundary is exact: Feb 1 00:00:00 enables next year.</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>#3322</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Create Validation</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Uses TimeUtils.today() — test with clock at 23:59 Jan 31 and 00:00 Feb 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-141</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Calendar change — existing vacation duration recalculation</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Employee in Office A with vacation request spanning Dec 22 - Jan 9.
+Office calendar currently uses Russian production calendar.
+Admin changes office to use Cyprus calendar (different holidays).</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1. Record vacation duration (working days) under Russian calendar.
+2. Change production calendar for the office.
+3. Verify vacation duration recalculated under new calendar.
+4. Check event feed for DAYS_PER_YEAR_CHANGED event.
+5. Check available vacation days recalculated.
+6. Try editing the vacation — verify no 'Calculation error'.</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Vacation duration recalculated if calendar change event is properly handled.
+If #2876 Bug 2 is present: editing/deleting may produce 'Calculation error'.
+Event feed should log the calendar change (if DAYS_PER_YEAR_CHANGED implemented).
+Available days should reflect new calendar's working days count.</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Calendar Integration</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>Bug 2 from #2876: type change or deletion after calendar switch triggers 'Calculation error'. Check if fixed in current build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-142</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>VacationStatusUpdateJob — APPROVED to PAID transition timing</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Employee has APPROVED vacation ending yesterday.
+VacationStatusUpdateJob runs every 10 minutes.</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>1. Create and approve a vacation ending today.
+2. Set clock to tomorrow.
+3. Wait up to 10 minutes for job execution.
+4. GET vacation status.
+5. Verify transition to PAID.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Vacation transitions from APPROVED to PAID after job runs.
+Maximum orphan window: 10 minutes.
+Status is PAID, not still APPROVED.</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Status Job</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>VacationStatusUpdateJob fixedDelay=600000ms. Test the timing window.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J15"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Suite: Maternity Leave Lifecycle — Begin/End Events, Day Adjustment, Edge Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-143</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Maternity begin — proportional current year day reduction</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Employee in AV=false office (norm=28 days/year).
+Employee has 28 available days for current year.
+Current date: September 15 (3.5 months remaining in year).</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1. Record employee_vacation.available_vacation_days before maternity.
+2. Trigger CS sync with maternity=true for the employee.
+3. DB: Check timeline for MATERNITY_BEGIN event.
+4. DB: Check employee_vacation for current year.
+5. Verify formula: subtract = 28 × (108 / 365) = 8.3 → HALF_UP → 8.
+6. Expected current year days: 28 - 8 = 20.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Current year days reduced from 28 to 20.
+Timeline event MATERNITY_BEGIN with days_accrued = -8.
+Formula: annualDays × remainingDays / totalYearDays, HALF_UP rounding.
+Remaining days counted from today to Dec 31 inclusive.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>EmployeeMaternityBeginEventListener. Real data: afanaseva maternity Sep 15 → accrued=-7 (28 × 107/365 = 8.2 → 8? Verify rounding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-144</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Maternity begin — next year days zeroed</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Employee has employee_vacation record for next year with 28 days.
+Employee enters maternity leave.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Verify employee_vacation for next year = 28 before maternity.
+2. Trigger maternity begin event.
+3. DB: Check employee_vacation for next year.
+4. Verify next year days = 0.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Next year available_vacation_days set to exactly 0.
+Timeline event records this change.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Production bug V2.1.25: race condition with annual accrual job re-set next year to 24 after zeroing. Verify no race.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-145</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Maternity end — proportional current year day restoration</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Employee on maternity leave (maternity=true).
+Office norm = 24 days/year.
+Maternity ends October 28 (~2 months remaining).</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Record employee_vacation for current year before maternity end.
+2. Trigger CS sync with maternity=false.
+3. DB: Check timeline for MATERNITY_END event.
+4. DB: Check employee_vacation for current year.
+5. Verify: restored days = vacationDaysHelpService.calculate(officeId, Oct28).
+6. Expected: ~24 × (64/365) ≈ 4 days added.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Current year days increased by ~4.
+Timeline event MATERNITY_END with days_accrued = +4.
+Calculation uses VacationDaysHelpService.calculate(officeId, endDate).
+Proportional accrual from maternity end date to year end.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Real data: apliskina maternity end Oct 28 → accrued=+4. Confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-146</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Maternity end — next year restored to full office allocation</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Employee on maternity with next year days = 0.
+Office annual leave for next year = 24.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Verify employee_vacation[next_year] = 0.
+2. Trigger maternity end event.
+3. DB: Check employee_vacation[next_year].
+4. Verify = office annual leave norm (24).</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Next year days restored to full office annual leave allocation (24).
+Uses officeAnnualLeaveService.getDays(officeId, nextYear).</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Real data: dshipacheva maternity end Dec 27 → 2026 days = 24 (full restore).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-147</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Maternity end near year-end — 0 days restored for current year</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Employee on maternity leave.
+Maternity ends December 27 (4 days before year end).</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>1. Set clock to December 27.
+2. Trigger maternity end event.
+3. DB: Check timeline MATERNITY_END event.
+4. DB: Check employee_vacation for current year.
+5. Verify: calculate(officeId, Dec27) ≈ 24 × 4/365 ≈ 0.
+6. DB: Check employee_vacation for next year = full allocation.</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Current year: days_accrued = 0 (too few remaining days).
+Next year: full allocation restored (24).
+Edge case: year-end maternity end adds 0 current-year days but full next-year.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Real data: dshipacheva maternity end 2025-12-27, accrued=0, 2026=24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-148</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Multi-year maternity — vacation day check across years</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Employee on maternity for 2+ years (e.g., 2023 to 2025).
+Has accumulated vacation days from before maternity.
+employee.maternity = true.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: SELECT year, available_vacation_days FROM employee_vacation WHERE employee = X.
+2. GET /api/vacation/v1/vacation/days/{employeeId}.
+3. Verify available = SUM of all years' available_vacation_days.
+4. Verify per-year view shows individual year balances.
+5. Create a vacation request — verify availability check uses total.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Available days = SUM across ALL years (not single-year check).
+VacationAvailabilityChecker.hasEnoughDaysForMaternityEmployee() sums all years.
+Employee can take vacation if total &gt; 0 even if current year = 0.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>VacationAvailabilityChecker: maternity employee uses total across all years instead of per-year strategy. Real data: iromanenko maternity since 2024-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-149</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Maternity — negative vacation days edge case</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Employee enters maternity with negative vacation balance.
+Current year available_vacation_days = -1.
+(Used more vacation than allocated before maternity)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Verify employee_vacation shows negative balance.
+2. Trigger maternity begin event.
+3. DB: Check current year days after reduction.
+4. Verify: balance goes further negative (current - subtractDays).
+5. DB: Check next year zeroed.
+6. Verify no error or exception from negative balance.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Maternity begin proceeds normally even with negative balance.
+Current year days become more negative.
+Next year zeroed to 0.
+No validation error — system allows negative days during maternity.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>Real data: mgrishkevich has -1 days while on maternity. zmustafina also at -1. System does not prevent this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-150</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Same-day maternity begin and end (CS sync correction)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>CS sync first sets maternity=true, then a correction sync sets maternity=false.
+Both events occur within minutes (same-day correction).</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1. Trigger CS sync with maternity=true.
+2. Wait for MATERNITY_BEGIN event processing.
+3. Immediately trigger CS sync with maternity=false.
+4. Wait for MATERNITY_END event processing.
+5. DB: Check employee_vacation for current and next year.
+6. DB: Check timeline for both events.</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Both events processed: BEGIN then END.
+Days reduced then restored — should approximately return to original.
+Possible rounding discrepancy: HALF_UP on reduction, different formula on restoration.
+Timeline shows both events with opposite accrued_days values.</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>#3370</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Real data: dprotopopova had BEGIN + END on 2024-09-25 (1.25 hours apart). accrued=-6 then +6. Same-day correction scenario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-151</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Maternity begin — annual accrual race condition (V2.1.25 bug)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Employee enters maternity in November.
+Next year days zeroed by MATERNITY_BEGIN event.
+Annual accrual job runs shortly after.</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>1. Set clock to November.
+2. Trigger CS sync with maternity=true.
+3. Verify next year days = 0.
+4. Trigger annual accrual job (POST /v1/test/vacation/annual-accruals).
+5. DB: Check employee_vacation for next year.
+6. Verify next year days still = 0 (not re-set to 24).</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>After annual accrual job, next year days remain 0.
+Accrual job must skip maternity employees' next year.
+If days reset to 24: PRODUCTION BUG (V2.1.25 regression).</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>V2.1.25, #3370</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>Production bug: mgrishkevich, edobrovlyanskaya, afanaseva had 2026 days incorrectly set to 24 after maternity begin. Fixed by manual migration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-152</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Office change during active maternity</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Employee on maternity leave (maternity=true).
+CS sync changes employee's salary office from Office A (norm=28) to Office B (norm=24).</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Record current employee_vacation days.
+2. Trigger CS sync with new office (different norm).
+3. DB: Check employee.office_id updated.
+4. DB: Check employee_vacation days — are they recalculated?
+5. GET /api/vacation/v1/vacation/days/{employeeId}.
+6. Check: which office norm would be used if maternity ends now?</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Office change processed (employee.office_id updated).
+Current vacation days may NOT be recalculated during maternity.
+When maternity ends: NEW office norm used for restoration.
+Potential discrepancy: days reduced with old norm, restored with new norm.</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>#2876, #3370</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Maternity + Office Sync</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Interaction between EmployeeOfficeChangedProcessor and maternity state. If norm differs: days were subtracted at old rate, restored at new rate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J13"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Suite: CS Office Settings — Unimplemented Features, Hardcoded Behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-153</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>First vacation restriction — verify 3-month hardcoded waiting period</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>New employee hired within the last 3 months.
+Employee has vacation days available (e.g., AV=true office).</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1. Find or create employee with hire date &lt; 3 months ago.
+2. POST /api/vacation/v1/vacation/create with valid vacation request.
+3. Check response for error about first vacation restriction.
+4. Set clock forward to 3 months + 1 day after hire.
+5. POST same vacation request.
+6. Verify success.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Before 3 months: vacation request rejected (if restriction enforced).
+After 3 months: vacation request accepted.
+NOTE: Verify if this restriction actually exists in code — #3026 says hardcoded to 3 but the actual enforcement point was not found in code analysis.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>#3026</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / CS Office Settings</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>CSSalaryOfficeVacationData.firstVacation exists in CS model but is NOT used in TTT. The 3-month restriction may be enforced differently or not at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-154</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation days carry-over — verify no expiration (burnOff unused)</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Employee with unused vacation days from 2+ years ago.
+Office has burnOff value set in CS but NOT used by TTT.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1. DB: Find employee with employee_vacation records for year Y-2.
+2. DB: Verify available_vacation_days &gt; 0 for year Y-2.
+3. GET /api/vacation/v1/vacation/days/{employeeId}.
+4. Verify: pastYearDays includes balance from Y-2 (no expiration).
+5. Create vacation consuming Y-2 days.
+6. Verify success — old days accepted.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation days from 2+ years ago are still available.
+No expiration logic applied — days carry over indefinitely.
+burnOff value from CS is completely ignored.
+FIFO consumption may apply (oldest year consumed first for AV=true).</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>#3026</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / CS Office Settings</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>CSSalaryOfficeVacationData.burnOff is defined but NOT synced or used. When implemented: test that days expire after configured months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-155</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>CS sync — unused fields not causing errors</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>CS returns all vacation data fields including firstVacation, burnOff, sickLeave.
+TTT only uses days, advanceVacation, overworkUnderwork.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1. Trigger CS sync: POST /v1/test/employee/sync.
+2. Verify sync completes without errors.
+3. DB: Check office table — no new columns for unused fields.
+4. DB: Check office.advance_vacation correctly updated.
+5. Check application logs for no warnings about unused fields.
+6. Verify office_annual_leave.days correctly synced.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Sync completes successfully.
+Unused CS fields (firstVacation, burnOff, sickLeave) silently ignored.
+Used fields (days, advanceVacation, overworkUnderwork) correctly synced.
+No errors or warnings in application logs.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>#3026</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / CS Office Sync</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>CSSalaryOfficeSynchronizer only processes 3 of 7 CS vacation fields. Remaining 4 ignored without error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-156</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Contractor sick leave eligibility — sickLeave setting unused</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Employee with contractor type in an office where CS has sickLeave=true.
+TTT does not use this setting.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1. Find contractor employee in the system.
+2. POST /api/vacation/v1/sickleave/create for the contractor.
+3. Check response — is contractor allowed to create sick leave?
+4. Compare with non-contractor in same office.
+5. Verify behavior is NOT affected by CS sickLeave setting.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Contractor sick leave behavior is uniform regardless of CS sickLeave value.
+Either all contractors can create sick leaves or none can.
+The CS sickLeave boolean has no effect on TTT behavior.
+Document actual contractor sick leave eligibility for future reference.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>#3026</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Sick Leave / CS Office Settings</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>CSSalaryOfficeVacationData.sickLeave is boolean in CS model. NOT used in TTT sick leave service. Verify contractor access rules.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J7"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Suite: Calendar Migration — Office Calendar Switch, Cross-Calendar Transfers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-157</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Office calendar migration — working day norm change verification</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Office migrated from Russia to Cyprus calendar in 2024.
+Example: Венера (id=10), Нептун (id=11), Уран (id=12).
+Different holidays between Russia and Cyprus calendars.</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1. DB (ttt_calendar): SELECT * FROM office_calendar WHERE office_id = 10.
+2. Verify: since_year=2023 → Russia, since_year=2024 → Cyprus.
+3. DB: Compare calendar_days for Russia vs Cyprus for same month.
+4. GET /api/calendar/v1/calendar/office/{officeId}?year=2023 (Russia).
+5. GET /api/calendar/v1/calendar/office/{officeId}?year=2024 (Cyprus).
+6. Compare working days count — different holidays should produce different norms.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>2023 calendar uses Russia holidays (e.g., Jan 1-8 = New Year break, May 9).
+2024 calendar uses Cyprus holidays (different holidays, different norms).
+Monthly working day counts differ between calendars.
+Vacation duration calculation uses the correct calendar for each year.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Calendar / Migration</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>11 offices migrated in 2024. Russia→Cyprus is the most common migration path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-158</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Employee vacation spanning calendar boundary year</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Employee in office that switched calendar (e.g., Венера: Russia→Cyprus in 2024).
+Vacation spans December 2023 → January 2024.</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1. Find or create vacation spanning Dec 2023 to Jan 2024 for office 10.
+2. Check: how are working days calculated?
+3. December 2023 days should use Russia calendar.
+4. January 2024 days should use Cyprus calendar.
+5. Verify total vacation duration = sum of both periods.
+6. Check if calendar boundary is handled correctly.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>December portion: working days counted using Russia calendar holidays.
+January portion: working days counted using Cyprus calendar holidays.
+Total duration correctly combines both calendars.
+If not: vacation may count wrong number of working days.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Calendar Integration</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>The since_year boundary in office_calendar determines which calendar applies. Cross-boundary vacations are a key risk area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-159</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Employee office transfer — same calendar offices (immediate update)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Employee moves from Сатурн (id=2, Russia cal) to Юпитер (id=4, Russia cal).
+Both offices use the same production calendar.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1. DB: Record employee_office for current year.
+2. Trigger CS sync with new office (Юпитер).
+3. DB: Check employee_office for current year — should update immediately.
+4. DB: Check employee.office_id — should match new office.
+5. Verify vacation day calculation uses new office annual leave norm.
+6. Check: no DEFERRED update since calendars are equal.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>employee_office updated immediately (same calendar = safe path).
+EmployeeOfficeChangedProcessor.isCalendarsAreEqual() returns true.
+Both employee.office_id and employee_office.office match new office.
+Vacation days recalculated with new office norm if different.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Office Transfer</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>Same-calendar transfer is the 'safe' path in EmployeeOfficeChangedProcessor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-160</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Employee office transfer — different calendar (deferred update)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Employee moves from Сатурн (id=2, Russia) to Венера (id=10, Cyprus) mid-year.
+Different production calendars.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1. Set clock to June (mid-year).
+2. DB: Record employee_office for current year.
+3. Trigger CS sync with new office (Венера, Cyprus calendar).
+4. DB: Check employee_office for CURRENT year — should NOT update.
+5. DB: Check employee_office for NEXT year — should update to new office.
+6. DB: Check employee.office_id — should update to new office.
+7. Verify: current year vacation uses OLD office norm.
+8. Verify: next year vacation will use NEW office norm.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Current year employee_office NOT updated (deferred — different calendar mid-year).
+Next year employee_office IS updated to new office.
+employee.office_id IS updated to new office.
+Current year: old calendar holidays used for vacation duration.
+Next year: new calendar holidays used.
+This is an intentional architectural decision.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>#2876</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Office Transfer</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>EmployeeOfficeChangedProcessor defers mid-year cross-calendar changes. This is the documented architectural decision — test the deferred path.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J7"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Suite: AV=True Multi-Year Balance Distribution (#3361)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-161</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>AV=true: Available days display shows availablePaidDays after multi-year vacation</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>AV=true office (e.g., Neptun SO, Cyprus/Germany).
+Employee has balance in both current year and next year.
+Find test data:
+  SELECT e.login, e.full_name, so.name AS office,
+         so.advance_vacation
+  FROM employee e
+  JOIN salary_office so ON e.salary_office_id = so.id
+  WHERE so.advance_vacation = true
+    AND e.enabled = true
+  LIMIT 5;
+Use timemachine env with clock set to second half of year (July-Nov).
+Employee should have available vacation days for current year.</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1. Navigate to Vacations page for the AV=true employee.
+2. Note the 'Available vacation days: X in YYYY' display.
+3. Create a vacation spanning Dec→Jan (e.g., 22.12.YYYY–11.01.YYYY+1).
+   Payment month: January YYYY+1.
+4. After creation, refresh the Vacations page.
+5. Check 'Available vacation days' display again.
+6. API: GET /api/vacation/v1/vacationdays/available?employeeLogin={login}
+   &amp;newDays=0&amp;usePaymentDateFilter=true
+7. Compare UI value with API response field `availablePaidDays`.
+8. Also check API response field `currentYear` — this should differ
+   from `availablePaidDays` if redistribution occurred.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>UI displays `availablePaidDays` value (NOT `currentYear`).
+After creating cross-year vacation:
+  - `availablePaidDays` correctly reflects redistributed balance.
+  - `currentYear` may show 0 or reduced value (pre-fix display).
+  - UI matches `availablePaidDays` from API response.
+  - Employee can still create vacations if availablePaidDays &gt; 0,
+    even if currentYear shows 0.
+BUG (pre-fix): UI showed `currentYear` = 0, blocking vacation creation
+even though `availablePaidDays` = 21.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>#3361, #3092</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Frontend / VacationEventsModal</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Core fix verification: MR !5169 changed userVacationDays.currentYear → userVacationDays.availablePaidDays in VacationEventsModal.js:120 and UserVacationsPage.js:102. This test verifies the fix is deployed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-162</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>AV=true: Vacation days display on main Vacations page uses availablePaidDays</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>AV=true office employee.
+Employee has vacations across multiple years.
+Use same employee as TC-VAC-161 or find another:
+  SELECT e.login, vdd.year, SUM(vdd.days) AS days_used
+  FROM employee e
+  JOIN vacation v ON e.id = v.employee_id
+  JOIN vacation_days_distribution vdd ON v.id = vdd.vacation_id
+  JOIN salary_office so ON e.salary_office_id = so.id
+  WHERE so.advance_vacation = true
+    AND v.status IN ('NEW', 'APPROVED')
+  GROUP BY e.login, vdd.year
+  ORDER BY e.login, vdd.year
+  LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to main Vacations page (UserVacationsPage).
+2. Locate the 'X in YYYY' display in the header/info section.
+3. API: GET /api/vacation/v1/vacationdays/available?employeeLogin={login}
+   &amp;newDays=0&amp;usePaymentDateFilter=true
+4. Verify the UI number matches API `availablePaidDays`.
+5. Create a new vacation in a future year.
+6. Refresh page and verify the display updates correctly.
+7. Cancel the vacation and verify display reverts.</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>UserVacationsPage displays `availablePaidDays` (not `currentYear`).
+Value updates dynamically after vacation create/cancel.
+Display format: '{availablePaidDays} in {currentYear}' where year is
+moment().format('YYYY').
+The `|| 0` fallback handles null/undefined values correctly.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>#3361</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Frontend / UserVacationsPage</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Second display location fixed by MR !5169: UserVacationsPage.js:102. Both modal and page must show `availablePaidDays`.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-163</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AV=true: Future vacations affect available days display</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>AV=true office employee with balance &gt; 21 days.
+No existing future-year vacations.
+Use timemachine env with clock in Oct-Nov of current year.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1. Navigate to Vacations page. Note 'Available days: X'.
+2. Create vacation in January of NEXT year (10 working days).
+   Payment month: January YYYY+1.
+3. After creation, refresh Vacations page.
+4. Verify 'Available days' decreased by approximately 10.
+5. API: GET /api/vacation/v1/vacationdays/available
+   Verify `availablePaidDays` reflects the future vacation deduction.
+6. Delete the future vacation.
+7. Verify 'Available days' increases back to original value.
+8. Check `vacation_days_distribution` table for year allocation.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Future vacations DO affect the `availablePaidDays` display.
+Creating 10-day vacation in next year reduces available by ~10.
+Deleting the vacation restores the balance.
+Sub-bug #3 from QA: if future vacations DON'T affect display,
+this is a remaining issue.
+`vacation_days_distribution` shows which year the days came from
+(FIFO: earliest year first).</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>#3361</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Balance / Display</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>QA sub-bug #3: omaksimova reported that future vacations don't affect the available days display. Verify whether this is fixed or still open. The fix (availablePaidDays) should account for future allocations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-164</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>AV=true: FIFO redistribution across year boundary — create Dec→Jan vacation</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>AV=true office employee.
+Employee has 21 days/year norm.
+Employee has NO existing vacations consuming current-year days.
+Use timemachine env with clock in second half of year.
+Find test data:
+  SELECT e.login, vdy.year, vdy.available_days
+  FROM employee e
+  JOIN vacation_days_per_year vdy ON e.id = vdy.employee_id
+  JOIN salary_office so ON e.salary_office_id = so.id
+  WHERE so.advance_vacation = true
+    AND vdy.available_days &gt; 15
+    AND e.enabled = true
+  ORDER BY vdy.year DESC
+  LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1. Record current balance per year:
+   SELECT year, available_days FROM vacation_days_per_year
+   WHERE employee_id = {id} ORDER BY year;
+2. Create vacation spanning Dec 22 → Jan 11 (approx 13 working days).
+   Payment month: January YYYY+1.
+3. After creation, check distribution:
+   SELECT vdd.year, vdd.days FROM vacation_days_distribution vdd
+   JOIN vacation v ON vdd.vacation_id = v.id
+   WHERE v.employee_id = {id}
+   ORDER BY v.start_date, vdd.year;
+4. Verify FIFO: current-year days consumed first.
+   For a Dec 22–Jan 11 vacation:
+   - YYYY days: working days in Dec (22-31) → ~6-8 days
+   - YYYY+1 days: working days in Jan (1-11) → ~5-7 days
+5. Check updated balance per year.
+6. API: GET /api/vacation/v1/vacationdays/available
+   Verify `availablePaidDays` reflects remaining balance.
+7. Verify the employee can still create vacations in YYYY
+   if current-year balance &gt; 0.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Vacation spanning year boundary correctly splits days:
+  - `vacation_days_distribution` has 2 rows: one per year.
+  - Current-year allocation: Dec working days from YYYY balance.
+  - Next-year allocation: Jan working days from YYYY+1 balance.
+FIFO applied: earliest-year days consumed first.
+Balance updated correctly for both years.
+`availablePaidDays` reflects remaining after redistribution.
+Employee NOT blocked from creating more YYYY vacations if balance remains.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>#3361, #3092</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Balance / Redistribution</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Core redistribution test. The bug was that the frontend showed 0 available days after cross-year vacation, even though backend correctly redistributed. Now tests both backend redistribution AND frontend display accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-165</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>AV=true: Edit multi-year vacation — redistribution recalculates across other vacations</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>AV=true office employee with 2+ existing vacations.
+At least one vacation spans year boundary or consumes next-year days.
+Find test data:
+  SELECT e.login, v.id, v.start_date, v.end_date, v.status,
+         vdd.year, vdd.days
+  FROM employee e
+  JOIN vacation v ON e.id = v.employee_id
+  JOIN vacation_days_distribution vdd ON v.id = vdd.vacation_id
+  JOIN salary_office so ON e.salary_office_id = so.id
+  WHERE so.advance_vacation = true
+    AND v.status IN ('NEW', 'APPROVED')
+  ORDER BY e.login, v.start_date
+  LIMIT 20;</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>1. Record baseline: all vacations + their year distributions.
+2. Edit the earliest vacation to shorten it by 5 days.
+3. Wait for recalculation to complete.
+4. Check all vacation distributions again:
+   SELECT v.id, v.start_date, v.end_date, vdd.year, vdd.days
+   FROM vacation v
+   JOIN vacation_days_distribution vdd ON v.id = vdd.vacation_id
+   WHERE v.employee_id = {id}
+   ORDER BY v.start_date, vdd.year;
+5. Verify that freed days from the shortened vacation were
+   redistributed to later vacations (FIFO).
+6. If a later vacation was using next-year days but current-year
+   days are now available, verify it shifts to current-year.
+7. API: GET /api/vacation/v1/vacationdays/available
+   Check updated availablePaidDays.</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Editing one vacation triggers redistribution across ALL vacations.
+FIFO recalculation: all REGULAR+EXACT days returned to pool,
+then re-distributed chronologically.
+Later vacations may shift from next-year to current-year days
+if current-year days become available.
+No ADMINISTRATIVE conversion unless genuinely insufficient days.
+vacation_days_distribution reflects updated allocations.
+availablePaidDays updated to reflect new state.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>#3361, #3347</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Balance / Redistribution</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Tests the recalculation engine (VacationRecalculationServiceImpl). Editing returns ALL regular days to pool then re-distributes. This is the complex case #3361 Case 2 described.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-166</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Redux: daysLimitation preserved as structured value (not formatted by safeToFixed)</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Any employee with vacation days data.
+Browser with React DevTools installed (or check via browser console).
+Use Chrome DevTools &gt; Sources &gt; search for 'daysLimitation'.</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to Vacations page for any employee.
+2. Open browser console (F12).
+3. Access Redux state:
+   window.__REDUX_STORE__.getState().myVacation
+   (or equivalent Redux DevTools inspection).
+4. Find the `daysLimitation` field in vacation days state.
+5. Verify it is NOT a formatted number string (e.g., '21.00').
+6. If daysLimitation is an object, verify its structure is preserved.
+7. If daysLimitation is null, verify it remains null (not 'NaN' or '0.00').
+8. Create a vacation and verify daysLimitation is still correct
+   after state update.</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>daysLimitation in Redux state preserves its original type from API:
+  - If object: properties intact (not '[object Object]' string).
+  - If null: remains null (not 'NaN' or formatted as '0.00').
+  - If number: raw number (not formatted with safeToFixed).
+BUG (pre-fix): safeToFixed() converted structured data to '0.00'
+or 'NaN', breaking vacation form validation logic.
+Other fields (currentYear, nextYear, reserved, etc.) still use
+safeToFixed correctly — only daysLimitation was affected.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>#3361</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Frontend / Redux Reducer</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>MR !5211 fix: removed safeToFixed() wrapper from daysLimitation in myVacation/reducer.ts:175. Verify via Redux DevTools or console.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-167</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>API: /v1/vacationdays/available returns correct availablePaidDays for AV=true</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>AV=true office employee.
+Employee has known vacation day balances.
+Use timemachine or qa-1 env.</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1. GET /api/vacation/v1/vacationdays/available?employeeLogin={login}
+   &amp;newDays=0&amp;usePaymentDateFilter=true
+2. Record response fields:
+   - availablePaidDays
+   - currentYear (raw year balance)
+   - daysNotEnough (array)
+3. DB: Cross-verify with vacation_days_per_year:
+   SELECT year, available_days, norm_days
+   FROM vacation_days_per_year
+   WHERE employee_id = {id} ORDER BY year;
+4. Create a vacation (21 days, payment month next year).
+5. Repeat the API call. Verify availablePaidDays decreased.
+6. Test with usePaymentDateFilter=false — compare results.
+7. Test with newDays=10 — verify it simulates adding 10 days
+   and returns adjusted available.
+8. Verify daysNotEnough array is populated when insufficient.</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>API returns correct `availablePaidDays`:
+  - Accounts for all existing NEW/APPROVED vacations.
+  - Reflects FIFO redistribution across years.
+  - `newDays` parameter simulates additional consumption.
+  - `usePaymentDateFilter=true` limits to payment-month-eligible days.
+  - `daysNotEnough` populated when balance insufficient.
+`currentYear` is the raw per-year balance (may differ from
+availablePaidDays due to cross-year redistribution).
+This endpoint is what the frontend now uses for display.</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>#3361, #3092</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / API / VacationDays</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>The BDD test from dev (snavrockiy) confirmed: POST vacation → distribution 2025:21 → balance 2025:0, 2026:21 → availablePaidDays returns 21.0 (not 0). This test verifies that contract on live environment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-168</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>AV=true/false: Waiting period tooltip for new and rehired employees</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Employee hired within last 3 months (within waiting period).
+Test on both AV=true and AV=false offices.
+Find test data:
+  SELECT e.login, e.full_name, ewp.first_working_day,
+         so.advance_vacation, so.name AS office
+  FROM employee e
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  JOIN salary_office so ON e.salary_office_id = so.id
+  WHERE ewp.first_working_day &gt; CURRENT_DATE - INTERVAL '90 days'
+    AND e.enabled = true
+  ORDER BY ewp.first_working_day DESC
+  LIMIT 10;
+Also find rehired employee (multiple work periods):
+  SELECT e.login, COUNT(*) AS periods
+  FROM employee e
+  JOIN employee_work_period ewp ON e.id = ewp.employee_id
+  WHERE e.enabled = true
+  GROUP BY e.id HAVING COUNT(*) &gt; 1
+  LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1. Navigate to Vacations page as the new employee (&lt; 3 months).
+2. Attempt to create a regular vacation.
+3. Verify a tooltip/message explains the 3-month waiting period.
+4. Check the tooltip text: should state that vacation is unavailable
+   until 3 months from first_working_day.
+5. Repeat for AV=false employee — same tooltip expected.
+6. For rehired employee (terminated then rehired next day):
+   - Navigate to Vacations page.
+   - Check if 3-month waiting period applies from re-hire date.
+   - Per clarification: period applies from first day of employment
+     (not the original hire date, but the new work period start).
+7. Verify administrative vacations are still allowed during
+   the waiting period (only regular blocked).</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>New employee (&lt; 3 months):
+  - Tooltip/message displayed explaining waiting period.
+  - Regular vacation creation blocked.
+  - Administrative vacation still allowed.
+AV=true AND AV=false: both show the same waiting period behavior.
+Rehired employee:
+  - 3-month period starts from new first_working_day (not original).
+  - If rehired day after termination, still waits 3 months.
+Sub-bug #4/#4.1: tooltip may NOT display (known sub-bug from QA).
+If tooltip is missing, document as remaining defect.</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>#3361</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Frontend / Waiting Period</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>QA sub-bugs #4 and #4.1: omaksimova reported missing tooltip for new employees and incorrect 3-month calculation for rehired employees. imalakhovskaia clarified: 3-month period from first employment day. snavrockiy said fix is merged but ticket still open.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J11"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="35" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Suite: Past-Date Validation &amp; Balance Fix (#3369, #3360)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>Requirement Ref</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Module/Component</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-169</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Update vacation start date to past — validation rejects</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Employee with an existing NEW or APPROVED vacation with start date in the future.
+Use timemachine env with clock set to a date between the current date and the vacation start.
+Find test data:
+  SELECT e.login, v.id, v.start_date, v.end_date, v.status
+  FROM ttt_vacation.employee e
+  JOIN ttt_vacation.vacation v ON e.id = v.employee_id
+  WHERE v.start_date &gt; CURRENT_DATE
+    AND v.status IN ('NEW', 'APPROVED')
+  ORDER BY v.start_date
+  LIMIT 5;
+Note: Advance clock so the vacation's start date is now in the past.</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>1. Record the existing vacation: id={id}, startDate={future_date}, endDate={end}.
+2. Advance the timemachine clock past the vacation's start_date:
+   PATCH /api/ttt/test/clock with date after the vacation's start.
+3. Attempt to update the vacation via API:
+   PUT /api/vacation/v1/vacations/{id}
+   Body: { login, startDate: {now_past_date}, endDate: {end}, paymentType: REGULAR, paymentMonth }
+   where startDate is the original (now in the past) start date.
+4. Verify response is 400 with validation error.
+5. Check error body contains 'validation.vacation.start.date.in.past'.
+6. Also attempt via UI: edit the vacation, change start date to yesterday.
+7. Verify the form shows validation error message.
+8. Verify the original vacation is unchanged in DB.</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>API returns 400 Bad Request.
+Error body contains: validation.vacation.start.date.in.past
+Error is attached to startDate field.
+The vacation entity is NOT modified in the database.
+UI shows validation error when attempting to save.
+Note: VacationUpdateValidator delegates to VacationCreateValidator.isStartEndDatesCorrect() — same check.</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>#3369, MR !5116</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / API / VacationUpdateValidator</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>Update validator delegates past-date check to create validator (line 187). BDD Scenario 3 (vacation.feature:607) covers this path. Runs for both AV=false and AV=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-170</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Past start date + end before start — both validation errors returned simultaneously</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Any active employee on timemachine env.
+Clock set to a known current date (e.g., 2026-03-15).</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1. Attempt to create vacation via API:
+   POST /api/vacation/v1/vacations
+   Body: {
+     login: {employee_login},
+     startDate: '2026-03-10',  // 5 days in past
+     endDate: '2026-03-05',    // before start date
+     paymentType: 'REGULAR',
+     paymentMonth: '2026-03-01'
+   }
+2. Verify response is 400 with MULTIPLE validation errors.
+3. Parse the error response body.
+4. Verify it contains BOTH:
+   a) 'validation.vacation.start.date.in.past' (on startDate field)
+   b) 'validation.vacation.dates.order' (on startDate AND endDate fields)
+5. Verify NO other validation errors (duration, next-year) are present.
+   These are short-circuited by &amp;&amp; after isStartEndDatesCorrect() fails.
+6. Try same via UI: enter past start date AND end date before start.
+7. Verify both errors are displayed (or check if frontend only shows first).</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>API returns 400 with TWO validation violations:
+  1. validation.vacation.start.date.in.past (on startDate)
+  2. validation.vacation.dates.order (on BOTH startDate and endDate)
+Both collected before method returns — non-short-circuiting within isStartEndDatesCorrect().
+Subsequent validations (duration, next-year) are NOT invoked.
+No vacation entity created.</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>#3369, MR !5116</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / API / VacationCreateValidator</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>BDD Scenario 2 (vacation.feature:584) verifies both errors returned. isStartEndDatesCorrect() collects all constraint violations in a single pass, then returns false. The &amp;&amp; short-circuits isValidVacationDuration and isNextVacationAvailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-171</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Boundary: vacation starting today accepted, starting yesterday rejected</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Active employee on timemachine env.
+Employee has sufficient vacation days balance.
+Clock set to a specific date (e.g., 2026-06-15).
+No overlapping vacations for the test dates.</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>1. Set timemachine clock to 2026-06-15T10:00:00.
+2. Create vacation starting TODAY (2026-06-15) to 2026-06-25:
+   POST /api/vacation/v1/vacations
+   { startDate: '2026-06-15', endDate: '2026-06-25', paymentType: REGULAR, ... }
+3. Verify response is 200 OK — vacation created successfully.
+4. Delete the vacation (or use a different employee for step 5).
+5. Create vacation starting YESTERDAY (2026-06-14) to 2026-06-25:
+   POST /api/vacation/v1/vacations
+   { startDate: '2026-06-14', endDate: '2026-06-25', paymentType: REGULAR, ... }
+6. Verify response is 400 with 'validation.vacation.start.date.in.past'.
+7. Verify via UI:
+   a) Open vacation creation form, set start date to today — Submit succeeds.
+   b) Open form, set start date to yesterday — Submit fails.
+8. Edge case: advance clock to 2026-06-15T23:59:59.
+   Create vacation starting 2026-06-15 — should still succeed.
+   The check uses LocalDate (date-only), not timestamp.</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Today's date is ACCEPTED — isBefore(today) returns false for today.
+Yesterday's date is REJECTED — isBefore(today) returns true.
+Validation uses LocalDate comparison (TimeUtils.today()),
+NOT timestamp-level — time of day does not affect the result.
+23:59:59 on today still allows today's date as start.
+This is a boundary condition: &gt;= today passes, &lt; today fails.</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>#3369, MR !5116</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / API / VacationCreateValidator</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>The validation uses startDate.isBefore(today) — strict less-than. Today is NOT 'before' today, so it passes. BDD Scenario 1 uses a 5-day gap (Jan 10 vs Jan 15). This test targets the exact boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>TC-VAC-172</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Past-date validation error displayed as raw key — missing frontend translation</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Active employee on timemachine env.
+Clock set to a date that makes the vacation's start in the past.
+Use Chrome browser with DevTools open (Network tab).</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1. Open vacation creation form in UI.
+2. Set start date to a past date (e.g., yesterday).
+3. Submit the form.
+4. Observe the error message displayed in the form.
+5. Check Network tab for the API response body.
+6. Compare API error key with displayed UI message.
+7. Check for these error keys in the UI:
+   a) 'validation.vacation.start.date.in.past' — expected: raw key or generic fallback
+   b) 'validation.vacation.dates.order' — expected: raw key or generic fallback
+   c) 'validation.vacation.next.year.not.available' — expected: raw key or generic fallback
+8. Compare with TRANSLATED error keys:
+   a) 'exception.validation.vacation.duration' — should show 'You don't have enough...'
+   b) 'exception.validation.vacation.too.early' — should show 'Vacation request can be...'
+9. Document the exact error message shown for each untranslated key.</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>KNOWN DEFECT: The following validation error keys have NO frontend translation:
+  - validation.vacation.start.date.in.past
+  - validation.vacation.dates.order
+  - validation.vacation.next.year.not.available
+UI displays the raw key string (e.g., 'validation.vacation.start.date.in.past')
+or a generic error fallback, depending on frontend error handling.
+Only these keys have translations:
+  - exception.validation.vacation.duration -&gt; 'You don't have enough available vacation days'
+  - exception.validation.vacation.too.early -&gt; 'Vacation request can be created after 6 months...'
+Document the actual UI behavior for each key.</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>#3369, MR !5116</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Vacation / Frontend / i18n</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Codebase grep confirmed: no translation entries for 'start.date.in.past', 'dates.order', 'next.year.not.available' in frontend i18n files. Only 'duration' and 'too.early' have proper translations. This is a UX defect — user sees a technical key string instead of human-readable message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>TC-VAC-173</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Expected year-end balance calculation — unbounded year sum (#3360 fix)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Employee with &gt; 2 years of employment and vacation accruals.
+Employee should have available_vacation_days in 3+ different years.
+Find test data (ttt_vacation DB):
+  SELECT ev.employee AS emp_id, COUNT(DISTINCT ev.year) AS year_count,
+         SUM(ev.available_vacation_days) AS total_days
+  FROM ttt_vacation.employee_vacation ev
+  GROUP BY ev.employee
+  HAVING COUNT(DISTINCT ev.year) &gt;= 3
+  ORDER BY SUM(ev.available_vacation_days) DESC
+  LIMIT 5;
+Then get the login:
+  SELECT login FROM ttt_vacation.employee WHERE id = {emp_id};
+Use timemachine env.</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>1. Record baseline per-year balances:
+   SELECT year, available_vacation_days
+   FROM ttt_vacation.employee_vacation
+   WHERE employee = {emp_id}
+   ORDER BY year;
+2. API: GET /api/vacation/v1/vacationdays/available?employeeLogin={login}
+   &amp;newDays=0&amp;usePaymentDateFilter=true
+3. Record `availablePaidDays` from response.
+4. Calculate expected: SUM of available_vacation_days WHERE year &lt;= current_year.
+   This should be an UNBOUNDED sum (no 3-year window).
+5. Verify API `availablePaidDays` matches the unbounded sum
+   (not the 3-year window sum).
+6. For an employee with 4+ years of accruals:
+   Old behavior (pre-fix): calculateDaysBeforeAndAfter(year, year-2) = 3-year window
+   New behavior: calculateDaysNotAfter(year) = all years &lt;= current
+7. If the employee has days in year-3 or earlier:
+   unbounded_sum SHOULD BE &gt; 3year_sum.
+8. UI: Navigate to Vacations page and verify 'Expected balance'
+   display reflects the full balance (not truncated to 3 years).</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>API `availablePaidDays` equals SUM of all available_vacation_days
+for year &lt;= current_year (unbounded, not 3-year window).
+For employee with 4+ years:
+  Pre-fix: balance missed year-3 and older accruals.
+  Post-fix: balance includes ALL historic accruals.
+SQL verification:
+  SELECT SUM(available_vacation_days) FROM employee_vacation
+  WHERE employee = {id} AND year &lt;= EXTRACT(YEAR FROM CURRENT_DATE)
+  should match API availablePaidDays (minus any pending vacations).
+UI 'Expected balance' reflects the full unbounded sum.</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>#3360, MR !5116</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Vacation / Backend / EmployeeDaysServiceImpl</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>Same MR !5116 as #3369. Changed calculateDaysBeforeAndAfter(year, year-2) to calculateDaysNotAfter(year). SQL changed from 'WHERE year &lt;= :before AND year &gt;= :after' to 'WHERE year &lt;= :year'. Affects VacationAvailablePaidDaysCalculatorImpl.calculate() line 94.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J8"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Vacation Module Test Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>&lt;- Back to Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>1. Recommended Test Users (Module-Specific)</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="30" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>User / Query</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Use perekrest or ilnitsky</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT+ADMIN</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>For vacation payment and admin actions</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Use alsmirnov</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>For basic vacation creation/view</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Use kcherenkov</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>PM+DEPT_MGR</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>For approval workflow testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>2. Common Multi-Role Test Users (All Modules)</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="30" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Login</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Best For</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>perekrest</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_ACCOUNTANT, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Best multi-role user (7 roles). Use for cross-role permission testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>pvaynmaster</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, CHIEF_OFFICER, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Multi-role with CHIEF_OFFICER. Use for highest-privilege scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>ilnitsky</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Admin+accountant combo. Use for accounting and admin tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT, ADMIN, DEPT_MGR, EMPLOYEE, HR, PM</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Same role set as ilnitsky. Use as second admin/accountant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>juliet_nekhor</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, HR, PM, VIEW_ALL</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Has VIEW_ALL. Use for read-only permission tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>kcherenkov</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>DEPT_MGR, EMPLOYEE, PM, TECH_LEAD</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tech Lead + PM. Use for planner/project management tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>alsmirnov</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>EMPLOYEE</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>EMPLOYEE-only. Use as minimum-privilege baseline user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>3. Common SQL Queries (User Discovery)</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="30" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Find EMPLOYEE-only users (minimum privilege)</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true
+GROUP BY e.id
+HAVING COUNT(*) = 1 AND MAX(r.role) = 'ROLE_EMPLOYEE'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Find active contractors</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_CONTRACTOR'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Find active project managers</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_PROJECT_MANAGER'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Find active accountants</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ACCOUNTANT'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Find active admins</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, e.full_name
+FROM employee e
+JOIN employee_global_roles r ON e.id = r.employee_id
+WHERE e.enabled = true AND r.role = 'ROLE_ADMIN'
+LIMIT 5;</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>ttt_backend</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Get current report/approve periods per office</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>SELECT o.id as office_id, o.name,
+       rp.start as report_period_start,
+       ap.start as approve_period_start
+FROM office o
+JOIN office_period rp ON o.report_period_id = rp.id
+JOIN office_period ap ON o.approve_period_id = ap.id
+ORDER BY o.id;</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>ttt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>4. Module-Specific SQL Queries</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="30" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>SQL Query</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Find employees with sufficient accrued days (AV=false offices)</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, ev.days as available_days, o.name as office
+FROM ttt_vacation.employee e
+JOIN ttt_vacation.employee_vacation ev ON e.id = ev.employee_id
+JOIN ttt_vacation.office o ON e.office_id = o.id
+WHERE ev.days &gt;= 5 AND o.advance_vacation = false
+AND e.login IN (SELECT login FROM ttt_backend.employee WHERE enabled = true)
+ORDER BY ev.days DESC LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Find employees in AV=true offices (advance vacation)</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, o.name as office
+FROM ttt_vacation.employee e
+JOIN ttt_vacation.office o ON e.office_id = o.id
+WHERE o.advance_vacation = true
+AND e.login IN (SELECT login FROM ttt_backend.employee WHERE enabled = true)
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Find vacations by status for testing transitions</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>SELECT v.id, v.login, v.status, v.start_date, v.end_date, v.payment_type
+FROM ttt_vacation.vacation v
+WHERE v.status IN ('NEW', 'APPROVED')
+AND v.start_date &gt; CURRENT_DATE
+ORDER BY v.status, v.start_date LIMIT 20;</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Find employees with their approvers (for approval flow)</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>SELECT e.login, m.login as manager_login
+FROM ttt_backend.employee e
+JOIN ttt_backend.employee m ON e.manager_id = m.id
+WHERE e.enabled = true AND m.enabled = true
+LIMIT 10;</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Find vacation days grouped by year (for balance testing)</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>SELECT ev.employee_id, e.login, ev.year, ev.days
+FROM ttt_vacation.employee_vacation ev
+JOIN ttt_vacation.employee e ON ev.employee_id = e.id
+WHERE ev.year &gt;= 2025
+ORDER BY e.login, ev.year;</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Run on timemachine/qa-1 DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>5. Data Generation Strategies</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="30" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Start date generation</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Use CURRENT_DATE + 14 days (next Monday after 2-week buffer). Format: YYYY-MM-DD. Always pick a Monday for 5-day vacation.</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>End date generation</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Start date + 4 days (Friday) for standard 5-day vacation. For boundary: use 1-day (same as start), cross-month, cross-year.</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Payment month</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>First of the month containing startDate. Format: YYYY-MM-01.</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Boundary values</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>0 days (expect error), 1 day, max allowed days, days &gt; available balance.</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>6. Environment Reference</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="n"/>
+      <c r="C44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>timemachine</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>https://ttt-timemachine.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Primary dev env — has test clock (PATCH to advance time)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>qa-1</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>https://ttt-qa-1.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Secondary dev env — real clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>https://ttt-stage.noveogroup.com</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Production-like env — read-only testing preferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>7. API Authentication</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="n"/>
+      <c r="C50" s="30" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>How to Obtain/Use</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>JWT (user context)</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Login via CAS SSO at /login, extract TTT_JWT_TOKEN cookie. Pass as Authorization: Bearer &lt;token&gt; or Cookie header.</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Most endpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>API token</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Set header API_SECRET_TOKEN: &lt;token_value&gt;. Value from env config file.</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Test/sync endpoints, limited scope</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A29:C29"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2769,7 +7184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2795,6 +7210,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -3049,25 +7465,79 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>AV Multi-Year Balance</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>TS-VAC-AVMultiYear</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Past-Date Validation</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="34" t="inlineStr">
+        <is>
+          <t>TS-VAC-PastDateVal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D13" s="11" t="n">
+      <c r="B15" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>130</v>
+      <c r="E15" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3084,6 +7554,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
